--- a/data/trans_orig/P6716-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82240</t>
+          <t>82912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89070</t>
+          <t>87280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49756</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93410</t>
+          <t>93556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131053</t>
+          <t>131569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127434</t>
+          <t>126788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160494</t>
+          <t>158758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>74797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99933</t>
+          <t>100248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211631</t>
+          <t>209124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253022</t>
+          <t>250614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>40674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88010</t>
+          <t>88991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>105335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145742</t>
+          <t>146266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82958</t>
+          <t>84386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119222</t>
+          <t>120481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71890</t>
+          <t>73705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136885</t>
+          <t>136960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182570</t>
+          <t>182206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188613</t>
+          <t>188578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231382</t>
+          <t>231223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117573</t>
+          <t>120172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151988</t>
+          <t>152989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320659</t>
+          <t>319298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376390</t>
+          <t>376565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27432</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46444</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74610</t>
+          <t>75759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62294</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87219</t>
+          <t>87391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127837</t>
+          <t>127276</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48923</t>
+          <t>48317</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78526</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65368</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94579</t>
+          <t>97026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>137096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154075</t>
+          <t>155556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192055</t>
+          <t>192914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>82122</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111500</t>
+          <t>113353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244508</t>
+          <t>246669</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>295512</t>
+          <t>296755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48999</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70271</t>
+          <t>70546</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105222</t>
+          <t>104252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61371</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91893</t>
+          <t>91985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>137311</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>188643</t>
+          <t>184996</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>97918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135373</t>
+          <t>138096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>62446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92081</t>
+          <t>92041</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166733</t>
+          <t>167510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215039</t>
+          <t>215029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>162152</t>
+          <t>161188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>204415</t>
+          <t>203194</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110032</t>
+          <t>109791</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143894</t>
+          <t>143803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282229</t>
+          <t>283452</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>336094</t>
+          <t>338595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87120</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77012</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>58554</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>125829</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>226886</t>
+          <t>228258</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>285938</t>
+          <t>288581</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>179451</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>231325</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>423210</t>
+          <t>422586</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>496707</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>317329</t>
+          <t>320767</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>390213</t>
+          <t>384439</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>198333</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>253605</t>
+          <t>249894</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>532829</t>
+          <t>535456</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>621080</t>
+          <t>617638</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>671257</t>
+          <t>675599</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>753581</t>
+          <t>751415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>413153</t>
+          <t>412159</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>475492</t>
+          <t>476624</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1111012</t>
+          <t>1112674</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1208422</t>
+          <t>1208325</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>46151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96616</t>
+          <t>98890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61618</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64169</t>
+          <t>64953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110126</t>
+          <t>109946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146818</t>
+          <t>147988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79604</t>
+          <t>79616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111300</t>
+          <t>109297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>45768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69737</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133261</t>
+          <t>131387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171006</t>
+          <t>169697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>33608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32916</t>
+          <t>32578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49446</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62594</t>
+          <t>61074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95256</t>
+          <t>95844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66654</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>109369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152409</t>
+          <t>152250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>103892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145651</t>
+          <t>141702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>67286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96583</t>
+          <t>98829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180235</t>
+          <t>182585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229370</t>
+          <t>231579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155631</t>
+          <t>156428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199018</t>
+          <t>198873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101469</t>
+          <t>100025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134662</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266464</t>
+          <t>267252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>320191</t>
+          <t>319662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>64633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104645</t>
+          <t>104743</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142616</t>
+          <t>142920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78595</t>
+          <t>77510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>110481</t>
+          <t>108409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190597</t>
+          <t>193968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>241041</t>
+          <t>240148</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>72473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106292</t>
+          <t>103923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>50416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77915</t>
+          <t>79132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130505</t>
+          <t>127547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172957</t>
+          <t>172530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91161</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126805</t>
+          <t>127338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172985</t>
+          <t>171474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220024</t>
+          <t>221588</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55230</t>
+          <t>55024</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85747</t>
+          <t>85325</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50818</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79553</t>
+          <t>80746</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>113415</t>
+          <t>113686</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156562</t>
+          <t>159995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90408</t>
+          <t>90091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124835</t>
+          <t>124441</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61122</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90204</t>
+          <t>91609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156914</t>
+          <t>160397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>204375</t>
+          <t>206520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180474</t>
+          <t>180101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>219574</t>
+          <t>219920</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128739</t>
+          <t>126974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163576</t>
+          <t>164142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317364</t>
+          <t>315894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372000</t>
+          <t>371128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35206</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66203</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119675</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66251</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>103171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82652</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>126075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>174615</t>
+          <t>178353</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>285785</t>
+          <t>285020</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>351781</t>
+          <t>346451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>216962</t>
+          <t>217748</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>274523</t>
+          <t>273258</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>521464</t>
+          <t>518717</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>604264</t>
+          <t>604195</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>361713</t>
+          <t>361422</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>432494</t>
+          <t>429420</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>245893</t>
+          <t>246588</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>301454</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>621082</t>
+          <t>619278</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>711192</t>
+          <t>709876</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>538483</t>
+          <t>542482</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>617169</t>
+          <t>615831</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>377272</t>
+          <t>373985</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>438026</t>
+          <t>436224</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>935274</t>
+          <t>930975</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1032868</t>
+          <t>1034850</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6716-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>35630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82912</t>
+          <t>80333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>59568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87280</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>27139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93556</t>
+          <t>95089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131569</t>
+          <t>131684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126788</t>
+          <t>127012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158758</t>
+          <t>159652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74797</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100248</t>
+          <t>101044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209124</t>
+          <t>208654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250614</t>
+          <t>251161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>30946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57786</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88991</t>
+          <t>91247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105335</t>
+          <t>106736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>147977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84386</t>
+          <t>82588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120481</t>
+          <t>120536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>45981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>74594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136960</t>
+          <t>136402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182206</t>
+          <t>183221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188578</t>
+          <t>189961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231223</t>
+          <t>234445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120172</t>
+          <t>118884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152989</t>
+          <t>154802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319298</t>
+          <t>321213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376565</t>
+          <t>376928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>41184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75759</t>
+          <t>77864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63502</t>
+          <t>63205</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87391</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>128945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48317</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97026</t>
+          <t>95797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137096</t>
+          <t>134474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155556</t>
+          <t>155330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192914</t>
+          <t>193133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82122</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113353</t>
+          <t>112914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246669</t>
+          <t>247194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296755</t>
+          <t>295619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32380</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>50367</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70546</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60622</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91985</t>
+          <t>93256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>137311</t>
+          <t>139081</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>184996</t>
+          <t>184625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97918</t>
+          <t>97457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138096</t>
+          <t>135343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>92237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167510</t>
+          <t>169875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215029</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161188</t>
+          <t>162200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>203194</t>
+          <t>203650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109791</t>
+          <t>107655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143803</t>
+          <t>145709</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283452</t>
+          <t>282876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>338595</t>
+          <t>337851</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>52659</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>86170</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>58554</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>126259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>228258</t>
+          <t>228725</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>288581</t>
+          <t>290790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177522</t>
+          <t>179181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>231237</t>
+          <t>232405</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>422586</t>
+          <t>424898</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>496707</t>
+          <t>506140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>320767</t>
+          <t>321746</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>384439</t>
+          <t>386097</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>198333</t>
+          <t>196910</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>249894</t>
+          <t>250654</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>535456</t>
+          <t>534020</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>617638</t>
+          <t>617194</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>672895</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>751415</t>
+          <t>751637</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>412159</t>
+          <t>413914</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>476624</t>
+          <t>477932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1112674</t>
+          <t>1107715</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1209447</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59775</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46151</t>
+          <t>46138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>66171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98890</t>
+          <t>98803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91244</t>
+          <t>91721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>40963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64953</t>
+          <t>64464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>110642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147988</t>
+          <t>149697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79616</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109297</t>
+          <t>110747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69600</t>
+          <t>69100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131387</t>
+          <t>132744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169697</t>
+          <t>171975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>25657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>49337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>61380</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95844</t>
+          <t>94482</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>67263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109369</t>
+          <t>108475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152250</t>
+          <t>153249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103892</t>
+          <t>105568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141702</t>
+          <t>145451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67286</t>
+          <t>67007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98829</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182585</t>
+          <t>181882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>231551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156428</t>
+          <t>154262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198873</t>
+          <t>196880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100025</t>
+          <t>102316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132480</t>
+          <t>134926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267252</t>
+          <t>268085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319662</t>
+          <t>322658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33527</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41581</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104743</t>
+          <t>105677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142920</t>
+          <t>143385</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77510</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108409</t>
+          <t>109263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193968</t>
+          <t>193386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240148</t>
+          <t>241398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72473</t>
+          <t>72724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103923</t>
+          <t>105129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>50909</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79132</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127547</t>
+          <t>129376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172530</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>89898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127338</t>
+          <t>127343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>70686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101575</t>
+          <t>101178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171474</t>
+          <t>171728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221588</t>
+          <t>219278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>23489</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>47748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>46821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55024</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85325</t>
+          <t>85976</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80746</t>
+          <t>81270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>113686</t>
+          <t>113906</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>159995</t>
+          <t>156762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90091</t>
+          <t>91122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>125096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61427</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160397</t>
+          <t>158362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206520</t>
+          <t>204955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180101</t>
+          <t>180383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>219920</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126974</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164142</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315894</t>
+          <t>316878</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371128</t>
+          <t>371028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63619</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76274</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119216</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>65926</t>
+          <t>65818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82653</t>
+          <t>82095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>172993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>283049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>351058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>217748</t>
+          <t>214512</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>273258</t>
+          <t>271533</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>518717</t>
+          <t>522129</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>604195</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>361422</t>
+          <t>359859</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>429420</t>
+          <t>427779</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>246588</t>
+          <t>242759</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>301066</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>619278</t>
+          <t>623402</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>709876</t>
+          <t>709259</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>542482</t>
+          <t>541249</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>615831</t>
+          <t>618291</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>373985</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>436224</t>
+          <t>439866</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,47 +7603,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>985952</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>933471</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1034456</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>42,06%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>985952</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>930975</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1034850</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>42,08%</t>
         </is>
       </c>
     </row>
